--- a/Term Lists/Make_from_WOS/queries/1.xlsx
+++ b/Term Lists/Make_from_WOS/queries/1.xlsx
@@ -1,50 +1,265 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkStation\PyhtonWorkStation\SmallTools\EndNote\Term Lists\Make_from_WOS\queries\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D529B4A4-B9AB-4373-98C4-21E2A4CE59C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1440" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="67">
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>ISO Abbreviation</t>
+  </si>
+  <si>
+    <t>JCR Abbreviation</t>
+  </si>
+  <si>
+    <t>Horticulture Research</t>
+  </si>
+  <si>
+    <t>Hortic. Res.-England</t>
+  </si>
+  <si>
+    <t>HORTIC RES-ENGLAND</t>
+  </si>
+  <si>
+    <t>Microbiological Research</t>
+  </si>
+  <si>
+    <t>Microbiol. Res.</t>
+  </si>
+  <si>
+    <t>MICROBIOL RES</t>
+  </si>
+  <si>
+    <t>European Journal of Plant Pathology</t>
+  </si>
+  <si>
+    <t>Eur. J. Plant Pathol.</t>
+  </si>
+  <si>
+    <t>EUR J PLANT PATHOL</t>
+  </si>
+  <si>
+    <t>Current Opinion in Food Science</t>
+  </si>
+  <si>
+    <t>Curr. Opin. Food Sci.</t>
+  </si>
+  <si>
+    <t>CURR OPIN FOOD SCI</t>
+  </si>
+  <si>
+    <t>Current Microbiology</t>
+  </si>
+  <si>
+    <t>Curr. Microbiol.</t>
+  </si>
+  <si>
+    <t>CURR MICROBIOL</t>
+  </si>
+  <si>
+    <t>Plant Physiology and Biochemistry</t>
+  </si>
+  <si>
+    <t>Plant Physiol. Biochem.</t>
+  </si>
+  <si>
+    <t>PLANT PHYSIOL BIOCH</t>
+  </si>
+  <si>
+    <t>Postharvest Biology and Technology</t>
+  </si>
+  <si>
+    <t>Postharvest Biol. Technol.</t>
+  </si>
+  <si>
+    <t>POSTHARVEST BIOL TEC</t>
+  </si>
+  <si>
+    <t>Food Control</t>
+  </si>
+  <si>
+    <t>FOOD CONTROL</t>
+  </si>
+  <si>
+    <t>BMC Plant Biology</t>
+  </si>
+  <si>
+    <t>BMC Plant Biol.</t>
+  </si>
+  <si>
+    <t>BMC PLANT BIOL</t>
+  </si>
+  <si>
+    <t>Frontiers in Plant Science</t>
+  </si>
+  <si>
+    <t>Front. Plant Sci.</t>
+  </si>
+  <si>
+    <t>FRONT PLANT SCI</t>
+  </si>
+  <si>
+    <t>Plant Disease</t>
+  </si>
+  <si>
+    <t>PLANT DIS.</t>
+  </si>
+  <si>
+    <t>PLANT DIS</t>
+  </si>
+  <si>
+    <t>Food Chemistry</t>
+  </si>
+  <si>
+    <t>Food Chem.</t>
+  </si>
+  <si>
+    <t>FOOD CHEM</t>
+  </si>
+  <si>
+    <t>International Journal of Food Microbiology</t>
+  </si>
+  <si>
+    <t>Int. J. Food Microbiol.</t>
+  </si>
+  <si>
+    <t>INT J FOOD MICROBIOL</t>
+  </si>
+  <si>
+    <t>Biological Control</t>
+  </si>
+  <si>
+    <t>Biol. Control</t>
+  </si>
+  <si>
+    <t>BIOL CONTROL</t>
+  </si>
+  <si>
+    <t>Physiological and Molecular Plant Pathology</t>
+  </si>
+  <si>
+    <t>Physiol. Mol. Plant Pathol.</t>
+  </si>
+  <si>
+    <t>PHYSIOL MOL PLANT P</t>
+  </si>
+  <si>
+    <t>Molecular Plant Pathology</t>
+  </si>
+  <si>
+    <t>Mol. Plant Pathol.</t>
+  </si>
+  <si>
+    <t>MOL PLANT PATHOL</t>
+  </si>
+  <si>
+    <t>Plant Biotechnology Journal</t>
+  </si>
+  <si>
+    <t>Plant Biotechnol. J.</t>
+  </si>
+  <si>
+    <t>PLANT BIOTECHNOL J</t>
+  </si>
+  <si>
+    <t>Annals of Botany</t>
+  </si>
+  <si>
+    <t>Ann. Bot.</t>
+  </si>
+  <si>
+    <t>ANN BOT-LONDON</t>
+  </si>
+  <si>
+    <t>Microbiome</t>
+  </si>
+  <si>
+    <t>MICROBIOME</t>
+  </si>
+  <si>
+    <t>JOURNAL OF FOOD MICROBIOLOGY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Int. J. Food Microbiol.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT J FOOD MICROBIOL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nature Reviews Chemistry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nat. Rev. Chem.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NAT REV CHEM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iMeta</t>
+  </si>
+  <si>
+    <t>iMeta</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IMETA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -68,14 +283,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -400,232 +626,279 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Full Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ISO Abbreviation</v>
-      </c>
-      <c r="C1" t="str">
-        <v>JCR Abbreviation</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Horticulture Research</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Hortic. Res.-England</v>
-      </c>
-      <c r="C2" t="str">
-        <v>HORTIC RES-ENGLAND</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Microbiological Research</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Microbiol. Res.</v>
-      </c>
-      <c r="C3" t="str">
-        <v>MICROBIOL RES</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>European Journal of Plant Pathology</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Eur. J. Plant Pathol.</v>
-      </c>
-      <c r="C4" t="str">
-        <v>EUR J PLANT PATHOL</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Current Opinion in Food Science</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Curr. Opin. Food Sci.</v>
-      </c>
-      <c r="C5" t="str">
-        <v>CURR OPIN FOOD SCI</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Current Microbiology</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Curr. Microbiol.</v>
-      </c>
-      <c r="C6" t="str">
-        <v>CURR MICROBIOL</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Plant Physiology and Biochemistry</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Plant Physiol. Biochem.</v>
-      </c>
-      <c r="C7" t="str">
-        <v>PLANT PHYSIOL BIOCH</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Postharvest Biology and Technology</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Postharvest Biol. Technol.</v>
-      </c>
-      <c r="C8" t="str">
-        <v>POSTHARVEST BIOL TEC</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Food Control</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Food Control</v>
-      </c>
-      <c r="C9" t="str">
-        <v>FOOD CONTROL</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>BMC Plant Biology</v>
-      </c>
-      <c r="B10" t="str">
-        <v>BMC Plant Biol.</v>
-      </c>
-      <c r="C10" t="str">
-        <v>BMC PLANT BIOL</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Frontiers in Plant Science</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Front. Plant Sci.</v>
-      </c>
-      <c r="C11" t="str">
-        <v>FRONT PLANT SCI</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Plant Disease</v>
-      </c>
-      <c r="B12" t="str">
-        <v>PLANT DIS.</v>
-      </c>
-      <c r="C12" t="str">
-        <v>PLANT DIS</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Food Chemistry</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Food Chem.</v>
-      </c>
-      <c r="C13" t="str">
-        <v>FOOD CHEM</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>International Journal of Food Microbiology</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Int. J. Food Microbiol.</v>
-      </c>
-      <c r="C14" t="str">
-        <v>INT J FOOD MICROBIOL</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Biological Control</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Biol. Control</v>
-      </c>
-      <c r="C15" t="str">
-        <v>BIOL CONTROL</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Physiological and Molecular Plant Pathology</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Physiol. Mol. Plant Pathol.</v>
-      </c>
-      <c r="C16" t="str">
-        <v>PHYSIOL MOL PLANT P</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Molecular Plant Pathology</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Mol. Plant Pathol.</v>
-      </c>
-      <c r="C17" t="str">
-        <v>MOL PLANT PATHOL</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Plant Biotechnology Journal</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Plant Biotechnol. J.</v>
-      </c>
-      <c r="C18" t="str">
-        <v>PLANT BIOTECHNOL J</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Annals of Botany</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Ann. Bot.</v>
-      </c>
-      <c r="C19" t="str">
-        <v>ANN BOT-LONDON</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Microbiome</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Microbiome</v>
-      </c>
-      <c r="C20" t="str">
-        <v>MICROBIOME</v>
-      </c>
-    </row>
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C23">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError sqref="A1:C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>